--- a/data/trans_orig/P1417-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2007</t>
+          <t>Población con diagnóstico de anemia en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>44176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51030</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1018747</t>
+          <t>1017550</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1029658</t>
+          <t>1029277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1269910</t>
+          <t>1270937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1292871</t>
+          <t>1293604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2295805</t>
+          <t>2295418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2319326</t>
+          <t>2319304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1683675</t>
+          <t>1683679</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1691791</t>
+          <t>1691722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1557202</t>
+          <t>1557450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1575368</t>
+          <t>1575071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3246318</t>
+          <t>3245958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3264829</t>
+          <t>3264795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541999</t>
+          <t>540831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463094</t>
+          <t>463383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474279</t>
+          <t>474253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1009613</t>
+          <t>1008436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1023952</t>
+          <t>1023772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73613</t>
+          <t>74177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56139</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3253841</t>
+          <t>3254465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3269786</t>
+          <t>3269199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3305584</t>
+          <t>3305020</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3335927</t>
+          <t>3335588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6565780</t>
+          <t>6565794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6599602</t>
+          <t>6601654</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2012</t>
+          <t>Población con diagnóstico de anemia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36643</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64024</t>
+          <t>64227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42033</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72283</t>
+          <t>72971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>961154</t>
+          <t>961177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>972485</t>
+          <t>972461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1273773</t>
+          <t>1273570</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1301154</t>
+          <t>1301758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2240157</t>
+          <t>2239469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2270407</t>
+          <t>2270321</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26463</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51194</t>
+          <t>52075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62069</t>
+          <t>61754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1948117</t>
+          <t>1948749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1959984</t>
+          <t>1960008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1702351</t>
+          <t>1701470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1727082</t>
+          <t>1727057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3655434</t>
+          <t>3655749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3684778</t>
+          <t>3684456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17554</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476000</t>
+          <t>475103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441077</t>
+          <t>440533</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>453684</t>
+          <t>453553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>921072</t>
+          <t>920212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933763</t>
+          <t>933758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78406</t>
+          <t>77324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117875</t>
+          <t>117272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91368</t>
+          <t>91830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132583</t>
+          <t>134877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3395037</t>
+          <t>3395264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3410748</t>
+          <t>3410619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3432098</t>
+          <t>3432701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3471567</t>
+          <t>3472649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6837172</t>
+          <t>6834878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6878387</t>
+          <t>6877925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2016</t>
+          <t>Población con diagnóstico de anemia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>18131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25264</t>
+          <t>25859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>48899</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>35308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60561</t>
+          <t>63523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>736409</t>
+          <t>736216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748744</t>
+          <t>748946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>944252</t>
+          <t>945761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>969396</t>
+          <t>968801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1688446</t>
+          <t>1685484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1715556</t>
+          <t>1713699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28653</t>
+          <t>29354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54468</t>
+          <t>54442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36425</t>
+          <t>35031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>63827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2061314</t>
+          <t>2060141</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2073354</t>
+          <t>2072861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1933832</t>
+          <t>1933858</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1959647</t>
+          <t>1958946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4000474</t>
+          <t>4000858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4028260</t>
+          <t>4029654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542762</t>
+          <t>541565</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530548</t>
+          <t>529946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544250</t>
+          <t>544160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075327</t>
+          <t>1074253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090055</t>
+          <t>1089850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>29736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69578</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106639</t>
+          <t>107551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86805</t>
+          <t>87031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129101</t>
+          <t>127225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3347535</t>
+          <t>3347882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3365728</t>
+          <t>3365765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3425461</t>
+          <t>3424549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3462522</t>
+          <t>3464140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6780617</t>
+          <t>6782493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6822913</t>
+          <t>6822687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2023</t>
+          <t>Población con diagnóstico de anemia en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28079</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>40888</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60885</t>
+          <t>61305</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59634</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83510</t>
+          <t>82634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>484769</t>
+          <t>485723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>499128</t>
+          <t>499456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>690418</t>
+          <t>689998</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>709991</t>
+          <t>710415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1180641</t>
+          <t>1181517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1204517</t>
+          <t>1206457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,17 +5915,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76231</t>
+          <t>76230</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>55823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98125</t>
+          <t>99528</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70073</t>
+          <t>72412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116750</t>
+          <t>117645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2260633</t>
+          <t>2260430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2276707</t>
+          <t>2277155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,17 +6028,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2158217</t>
+          <t>2158218</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2136323</t>
+          <t>2134920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2179343</t>
+          <t>2178625</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4405108</t>
+          <t>4404213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4451785</t>
+          <t>4449446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>34674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>20717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>38562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641799</t>
+          <t>641309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625168</t>
+          <t>625789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642804</t>
+          <t>641396</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1268576</t>
+          <t>1268524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1286181</t>
+          <t>1286369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50050</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124397</t>
+          <t>124417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178242</t>
+          <t>177907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162598</t>
+          <t>160076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220423</t>
+          <t>221616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3396831</t>
+          <t>3396380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3419559</t>
+          <t>3419911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3467972</t>
+          <t>3468307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3521817</t>
+          <t>3521797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6872672</t>
+          <t>6871479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6930497</t>
+          <t>6933019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1417-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51417</t>
+          <t>51157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1017550</t>
+          <t>1018680</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1029277</t>
+          <t>1029640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1270937</t>
+          <t>1270980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1293604</t>
+          <t>1292842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2295418</t>
+          <t>2295678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2319304</t>
+          <t>2319453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>35869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1683679</t>
+          <t>1683580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1691722</t>
+          <t>1691705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1557450</t>
+          <t>1557709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1575071</t>
+          <t>1575353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3245958</t>
+          <t>3245217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3264795</t>
+          <t>3265188</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540831</t>
+          <t>540435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463383</t>
+          <t>463504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474253</t>
+          <t>474232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1008436</t>
+          <t>1009823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1023772</t>
+          <t>1023901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43609</t>
+          <t>43731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74177</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54087</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>89366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3254465</t>
+          <t>3254200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3269199</t>
+          <t>3269219</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3305020</t>
+          <t>3304197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3335588</t>
+          <t>3335466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6565794</t>
+          <t>6566375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6601654</t>
+          <t>6601682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>36988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64227</t>
+          <t>65080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72971</t>
+          <t>74234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>961177</t>
+          <t>962086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>972461</t>
+          <t>972521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1273570</t>
+          <t>1272717</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1301758</t>
+          <t>1300809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2239469</t>
+          <t>2238206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2270321</t>
+          <t>2270627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52075</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>32892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61754</t>
+          <t>59792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1948749</t>
+          <t>1949002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1960008</t>
+          <t>1960310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1701470</t>
+          <t>1701718</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1727057</t>
+          <t>1727142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3655749</t>
+          <t>3657711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3684456</t>
+          <t>3684611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475103</t>
+          <t>476011</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>440533</t>
+          <t>440220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>453553</t>
+          <t>453498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>920212</t>
+          <t>920290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933758</t>
+          <t>933784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77324</t>
+          <t>79458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117272</t>
+          <t>119148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91830</t>
+          <t>91978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134877</t>
+          <t>133871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3395264</t>
+          <t>3395662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3410619</t>
+          <t>3410716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3432701</t>
+          <t>3430825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3472649</t>
+          <t>3470515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6834878</t>
+          <t>6835884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6877925</t>
+          <t>6877777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18131</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25859</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>33817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63523</t>
+          <t>60784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>736216</t>
+          <t>736649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748946</t>
+          <t>748891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>945761</t>
+          <t>944865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>968801</t>
+          <t>970418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1685484</t>
+          <t>1688223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1713699</t>
+          <t>1715190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29354</t>
+          <t>29884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54442</t>
+          <t>54162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35031</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63827</t>
+          <t>63147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2060141</t>
+          <t>2061074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2072861</t>
+          <t>2073226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1933858</t>
+          <t>1934138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1958946</t>
+          <t>1958416</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4000858</t>
+          <t>4001538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4029654</t>
+          <t>4029323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541565</t>
+          <t>541798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>529946</t>
+          <t>529674</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544160</t>
+          <t>544067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1074253</t>
+          <t>1075748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089850</t>
+          <t>1090943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29736</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>69394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107551</t>
+          <t>106898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87031</t>
+          <t>84949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127225</t>
+          <t>126825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3347882</t>
+          <t>3347703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3365765</t>
+          <t>3365656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3424549</t>
+          <t>3425202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3464140</t>
+          <t>3462706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6782493</t>
+          <t>6782893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6822687</t>
+          <t>6824769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -5537,27 +5537,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19543</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>15073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27125</t>
+          <t>30478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40888</t>
+          <t>45535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>66919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70075</t>
+          <t>76893</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>63273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82634</t>
+          <t>91102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -5650,22 +5650,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>493305</t>
+          <t>554939</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485723</t>
+          <t>545697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>499456</t>
+          <t>561102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>700771</t>
+          <t>763646</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>689998</t>
+          <t>752384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>710415</t>
+          <t>773768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1194076</t>
+          <t>1318584</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1181517</t>
+          <t>1304375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1206457</t>
+          <t>1332204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512848</t>
+          <t>576175</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512848</t>
+          <t>576175</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512848</t>
+          <t>576175</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751303</t>
+          <t>819303</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751303</t>
+          <t>819303</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751303</t>
+          <t>819303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264151</t>
+          <t>1395477</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264151</t>
+          <t>1395477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264151</t>
+          <t>1395477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26980</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76230</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55823</t>
+          <t>69332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99528</t>
+          <t>102937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>93389</t>
+          <t>103977</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72412</t>
+          <t>85236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117645</t>
+          <t>124134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2270252</t>
+          <t>2207745</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2260430</t>
+          <t>2198401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2277155</t>
+          <t>2215058</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2158218</t>
+          <t>2083493</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2134920</t>
+          <t>2064922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2178625</t>
+          <t>2098527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4428469</t>
+          <t>4291238</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4404213</t>
+          <t>4271081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4449446</t>
+          <t>4309979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2287410</t>
+          <t>2227356</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2287410</t>
+          <t>2227356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2287410</t>
+          <t>2227356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234448</t>
+          <t>2167859</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234448</t>
+          <t>2167859</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234448</t>
+          <t>2167859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4521858</t>
+          <t>4395215</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4521858</t>
+          <t>4395215</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4521858</t>
+          <t>4395215</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>28461</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>20516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38562</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6336,17 +6336,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>644722</t>
+          <t>709539</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641309</t>
+          <t>705991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646060</t>
+          <t>711007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>634152</t>
+          <t>706416</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625789</t>
+          <t>696215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641396</t>
+          <t>714361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1278874</t>
+          <t>1415955</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1268524</t>
+          <t>1405096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1286369</t>
+          <t>1424517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>42895</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>32641</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>55913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>153074</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124417</t>
+          <t>146827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177907</t>
+          <t>189557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>191676</t>
+          <t>211378</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160076</t>
+          <t>188054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>221616</t>
+          <t>240887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3408279</t>
+          <t>3472223</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3396380</t>
+          <t>3459205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3419911</t>
+          <t>3482477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3493140</t>
+          <t>3553555</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3468307</t>
+          <t>3532482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3521797</t>
+          <t>3575212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6901419</t>
+          <t>7025779</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6871479</t>
+          <t>6996270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6933019</t>
+          <t>7049103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3446881</t>
+          <t>3515118</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3446881</t>
+          <t>3515118</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3446881</t>
+          <t>3515118</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3646214</t>
+          <t>3722039</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3646214</t>
+          <t>3722039</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3646214</t>
+          <t>3722039</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7093095</t>
+          <t>7237157</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7093095</t>
+          <t>7237157</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7093095</t>
+          <t>7237157</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
